--- a/reports/2026-10-17/public_scholarships_report_2026-10-17.xlsx
+++ b/reports/2026-10-17/public_scholarships_report_2026-10-17.xlsx
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-17 07:40 PKT</t>
+          <t>2026-10-17 07:59 PKT</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RUN-20261017-074058</t>
+          <t>RUN-20261017-075906</t>
         </is>
       </c>
     </row>

--- a/reports/2026-10-17/public_scholarships_report_2026-10-17.xlsx
+++ b/reports/2026-10-17/public_scholarships_report_2026-10-17.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Report Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active Opportunities'!$A$1:$R$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Priority Highlights'!$A$1:$R$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'International'!$A$1:$R$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Watchlist (Awaiting Call)'!$A$1:$R$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Active Opportunities'!$A$1:$R$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Priority Highlights'!$A$1:$R$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'International'!$A$1:$R$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Watchlist (Awaiting Call)'!$A$1:$R$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -613,7 +613,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0002</t>
+          <t>SCH-202610-0071</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0001</t>
+          <t>SCH-202610-0070</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -793,22 +793,22 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0022</t>
+          <t>SCH-202610-0065</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>University of Peshawar Need-Based &amp; Fee Waiver Aid 2026-27</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>University of Peshawar Students Financial Aid Office</t>
+          <t>Ministry of Religious Affairs &amp; Interfaith Harmony</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>federal govt</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -818,15 +818,15 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>75</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -836,37 +836,37 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50% to 100% tuition fee waiver</t>
+          <t>Rs. 60,000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>University of Peshawar (UoP)</t>
+          <t>government educational institutions in Pakistan</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate (BS 4-Year), Master's, MPhil, PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Satisfactory academic performance and attendance</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>PKR 50,000 per month</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>https://www.uop.edu.pk/sfao/apply</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -876,29 +876,29 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>https://www.uop.edu.pk/sfao/</t>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0023</t>
+          <t>SCH-202610-0009</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>UET Peshawar Directorate of Financial Aid Need-cum-Merit Scholarship</t>
+          <t>Rehmatul Lil Alameen Scholarship for Dini Madaris 2026 (رحمت اللعالمین ﷺ اسکالرشپ برائے دینی مدارس)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>University of Engineering and Technology Peshawar</t>
+          <t>Auqaf, Hajj, Religious &amp; Minority Affairs Department</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>provincial govt</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -908,15 +908,15 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-03-25</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>159</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -926,37 +926,37 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Full tuition fee reimbursement plus semester book allowance</t>
+          <t>Rs. 100,000</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>UET Peshawar (Main &amp; satellite campuses)</t>
+          <t>Registered Dini Madaris of Khyber Pakhtunkhwa</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>BSc Engineering, Computer Science, Architecture</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2.50 CGPA in previous semester</t>
+          <t>Merit-based</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>PKR 55,000 per month</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>https://uetpeshawar.edu.pk/financial-aid/</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -966,29 +966,29 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>https://uetpeshawar.edu.pk/financial-aid/</t>
+          <t>https://scholarships.kpitb.online/#laptopScheme</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0025</t>
+          <t>SCH-202610-0054</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>IMSciences Peshawar Need-Based &amp; Financial Assistance Scheme</t>
+          <t>KPEF</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Institute of Management Sciences (IMSciences) Peshawar</t>
+          <t>KP Government / KP Education Foundation</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>provincial govt</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -998,15 +998,15 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2028-12-01</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>776</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Up to 100% tuition fee waiver plus semester assistance</t>
+          <t>Rs. 70</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>IMSciences Peshawar</t>
+          <t>Agriculture University Swat</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>BBA, BS Computer Science, BS Economics, MBA, MS</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2.50 CGPA and satisfactory conduct</t>
+          <t>minimum of 3 GPA</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>PKR 50,000 per month</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>https://imsciences.edu.pk/financial-aid/</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1056,29 +1056,29 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>https://imsciences.edu.pk/financial-aid/</t>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0024</t>
+          <t>SCH-202610-0082</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>KPEF Chief Minister Higher Education Scholarship Scheme 2026</t>
+          <t>University of Peshawar Need-Based &amp; Fee Waiver Aid 2026-27</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+          <t>University of Peshawar Students Financial Aid Office</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>provincial govt</t>
+          <t>university</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1088,11 +1088,11 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-11-25</t>
+          <t>2026-11-10</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -1106,37 +1106,37 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Full tuition fee and PKR 5,000 monthly stipend</t>
+          <t>50% to 100% tuition fee waiver</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>All HEC-recognized public and private universities in KP and top national institutions</t>
+          <t>University of Peshawar (UoP)</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>BS, MS, MPhil</t>
+          <t>Undergraduate (BS 4-Year), Master's, MPhil, PhD</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Minimum 65% marks in Intermediate or 3.00 CGPA</t>
+          <t>Satisfactory academic performance and attendance</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>PKR 60,000 per month</t>
+          <t>PKR 50,000 per month</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>https://scholarships.kpitb.online/</t>
+          <t>https://www.uop.edu.pk/sfao/apply</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,49 +1146,47 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/</t>
+          <t>https://www.uop.edu.pk/sfao/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0004</t>
+          <t>SCH-202610-0083</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ihsan Trust Qarz-e-Hasna Facility for Higher Education</t>
+          <t>UET Peshawar Directorate of Financial Aid Need-cum-Merit Scholarship</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Ihsan Trust</t>
+          <t>University of Engineering and Technology Peshawar</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>NGO-foundation</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Rolling / ongoing</t>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Rolling / ongoing</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1198,37 +1196,37 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100% tuition fee loan paid directly to the university</t>
+          <t>Full tuition fee reimbursement plus semester book allowance</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Over 150 partner universities including public and private universities in KP</t>
+          <t>UET Peshawar (Main &amp; satellite campuses)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate, Postgraduate</t>
+          <t>BSc Engineering, Computer Science, Architecture</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Good academic performance with minimum 2.50 CGPA</t>
+          <t>Minimum 2.50 CGPA in previous semester</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>PKR 55,000 per month</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>https://www.ihsantrust.org/apply-now/</t>
+          <t>https://uetpeshawar.edu.pk/financial-aid/</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1238,45 +1236,43 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>https://www.ihsantrust.org/education-loan/</t>
+          <t>https://uetpeshawar.edu.pk/financial-aid/</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0026</t>
+          <t>SCH-202610-0085</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Ihsan Trust Qarz-e-Hasna Interest-Free Student Loan</t>
+          <t>IMSciences Peshawar Need-Based &amp; Financial Assistance Scheme</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Ihsan Trust</t>
+          <t>Institute of Management Sciences (IMSciences) Peshawar</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>NGO-foundation</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Rolling / ongoing</t>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Rolling / ongoing</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>35</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1295,32 +1291,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100% university tuition fee paid directly to the university</t>
+          <t>Up to 100% tuition fee waiver plus semester assistance</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Over 150 partner universities across Pakistan (both public and private sectors in KP)</t>
+          <t>IMSciences Peshawar</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate, Master's, Professional Degrees</t>
+          <t>BBA, BS Computer Science, BS Economics, MBA, MS</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2.50 CGPA in previous semester</t>
+          <t>Minimum 2.50 CGPA and satisfactory conduct</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>PKR 50,000 per month</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>https://www.ihsantrust.org/education-loan/</t>
+          <t>https://imsciences.edu.pk/financial-aid/</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1330,49 +1326,47 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>https://www.ihsantrust.org/education-loan/</t>
+          <t>https://imsciences.edu.pk/financial-aid/</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0018</t>
+          <t>SCH-202610-0084</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>75th Celebration of Independence Day of Pakistan Scholarship Program</t>
+          <t>KPEF Chief Minister Higher Education Scholarship Scheme 2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Government of Pakistan</t>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>federal govt</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>2026-11-25</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1387,32 +1381,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Full tuition fee and PKR 5,000 monthly stipend</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>world's top 25 ranked universities</t>
+          <t>All HEC-recognized public and private universities in KP and top national institutions</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>MS and PhD</t>
+          <t>BS, MS, MPhil</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>world's top 25 ranked universities</t>
+          <t>Minimum 65% marks in Intermediate or 3.00 CGPA</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>PKR 60,000 per month</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>https://eportal.hec.gov.pk/idps75</t>
+          <t>https://scholarships.kpitb.online/</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1422,7 +1416,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>https://www.hec.gov.pk/english/scholarshipsgrants/IDPS/Pages/default.aspx</t>
+          <t>https://ef.kp.gov.pk/</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1428,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CM Foreign Scholarship</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1447,29 +1441,27 @@
           <t>provincial govt</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1479,12 +1471,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Rs. 60,000</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>University of Swabi</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1494,7 +1486,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Need-based</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1504,7 +1496,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1514,49 +1506,47 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/</t>
+          <t>https://scholarships.kpitb.online/#laptopScheme</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0017</t>
+          <t>SCH-202610-0028</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Chief Minister Foreign Scholarship Program</t>
+          <t>Climate Change and Mountain Agriculture Scholarship</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Chief Minister of Khyber Pakhtunkhwa through Khyber Pakhtunkhwa Education Foundation</t>
+          <t>Agriculture University Swat</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>provincial govt</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1571,22 +1561,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Rs. 100</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>selected universities in the People's Republic of China</t>
+          <t>University of Agriculture, Swat</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Culture, BS, MS, and PhD Programs</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>merit cum in-affordability basis</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1596,7 +1586,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>https://scholarships.kpitb.online/media/147/tors-climate-change.docx</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1606,49 +1596,47 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0012</t>
+          <t>SCH-202610-0026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Chief Minister's Free Laptop Distribution Scheme</t>
+          <t>Diversity &amp; Inclusion Scholarship</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Higher Education, Archives and Libraries Department</t>
+          <t>Agriculture University Swat</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>provincial govt</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>2027-01-01</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1663,22 +1651,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Rs. 100</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>approved universities/colleges</t>
+          <t>University of Agriculture, Swat (UoAS)</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>100% merit-based distribution, high-achieving and deserving enrolled students</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1688,7 +1676,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>https://scholarships.kpitb.online/student/laptop</t>
+          <t>https://scholarships.kpitb.online/media/148/tors-diversity.docx</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1698,49 +1686,47 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>https://scholarships.kpitb.online/</t>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0019</t>
+          <t>SCH-202610-0023</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Faculty Development Programme for Pakistani Universities</t>
+          <t>Agriculture University Swat Scholarship</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Higher Education Commission, Pakistan</t>
+          <t>Agriculture University Swat</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>federal govt</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>2027-12-01</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1755,17 +1741,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Rs. 142</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>HEC recognized universities/DAIs</t>
+          <t>Agriculture University Swat</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1780,7 +1766,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/FDP.aspx</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1790,49 +1776,47 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/default.aspx</t>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0009</t>
+          <t>SCH-202610-0029</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>KP Youth Scholarship</t>
+          <t>Disable Scholarship</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+          <t>Agriculture University Swat</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>provincial govt</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>2029-01-01</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>807</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1847,22 +1831,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Rs. 80</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>HE Government Colleges in Khyber Pakhtunkhwa</t>
+          <t>University of Agriculture, Swat (UoAS)</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>good academic merit</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1872,7 +1856,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/youth_scholarship</t>
+          <t>https://scholarships.kpitb.online/media/146/isable-tors-kpitb.docx</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -1882,43 +1866,45 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/</t>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0007</t>
+          <t>SCH-202610-0073</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Merit Cum Inaffordability Scholarship</t>
+          <t>Ihsan Trust Qarz-e-Hasna Facility for Higher Education</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+          <t>Ihsan Trust</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>provincial govt</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>NGO-foundation</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Rolling / ongoing</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>-305</v>
+          <t>Rolling / ongoing</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -1937,32 +1923,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>100% tuition fee loan paid directly to the university</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>approved list of Educational Institutions (Available on official website) within Pakistan</t>
+          <t>Over 150 partner universities including public and private universities in KP</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>BS &amp; MS</t>
+          <t>Undergraduate, Postgraduate</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Student must have scored at least 70% marks in the last attended examination or 3.00 CGPA in each semester, in case of arts specialized university selection will be on the basis of merit aptitude test where selection is on the basis of skills.</t>
+          <t>Good academic performance with minimum 2.50 CGPA</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Rs: 160,000/- per month</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/merit_cum_inaffordability</t>
+          <t>https://www.ihsantrust.org/apply-now/</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -1972,104 +1958,1482 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/</t>
+          <t>https://www.ihsantrust.org/education-loan/</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0014</t>
+          <t>SCH-202610-0086</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Türkiye Scholarships</t>
+          <t>Ihsan Trust Qarz-e-Hasna Interest-Free Student Loan</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Türkiye Scholarships (YTB)</t>
+          <t>Ihsan Trust</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>NGO-foundation</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Rolling / ongoing</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Rolling / ongoing</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>100% university tuition fee paid directly to the university</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Over 150 partner universities across Pakistan (both public and private sectors in KP)</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate, Master's, Professional Degrees</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Minimum 2.50 CGPA in previous semester</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ihsantrust.org/education-loan/</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ihsantrust.org/education-loan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0079</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>75th Celebration of Independence Day of Pakistan Scholarship Program</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Government of Pakistan</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>federal govt</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Deadline not stated</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>6.500 TL at Associate's and Bachelor's levels, 9.500 TL at Master's level and 13.000 TL at PhD level per month.</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>prestigious universities in Türkiye</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>associate, bachelor's, master’s, PhD and research degrees</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>The scholarship program is competitive and merit-based, with a strong emphasis on candidates’ academic excellence</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>https://tbbs.turkiyeburslari.gov.tr</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>world's top 25 ranked universities</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>MS and PhD</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>world's top 25 ranked universities</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>https://eportal.hec.gov.pk/idps75</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>https://turkiyeburslari.gov.tr/</t>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/IDPS/Pages/default.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0075</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>CM Foreign Scholarship</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0006</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Chief Minister Foreign Scholarship Program</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Government of Khyber Pakhtunkhwa / Khyber Pakhtunkhwa Education Foundation</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>selected universities in the People's Republic of China</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Language &amp; Culture, BS, MS, and PhD Programs</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>merit cum in-affordability basis</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0003</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Chief Minister's Free Laptop Distribution Scheme</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education, Archives and Libraries Department</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>approved universities/colleges</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>100% merit-based distribution across all 35 KP districts and approved universities/colleges</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/student/laptop</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0022</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Chief Minister's Honhaar Scholarship Program</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Bacha Khan University</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 91,550</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Bacha Khan University</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0080</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Faculty Development Programme for Pakistani Universities</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission, Pakistan</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>HEC recognized universities/DAIs</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/FDP.aspx</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/default.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0060</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Girls Stipend Programme</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 4,500</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>80% attendance</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0067</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>HEC Internation National Scholarships</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/InternationalScholarships.aspx</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0066</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>HEC National Scholarships</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/NationalScholarships.aspx</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0059</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Rehmat Ul Lil Alamin</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 50,000</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0058</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Stoori Da Pakhtunkhwa Program</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 15,000</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Top twenty position holders of Government Schools in SSC and HSSC exams</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0057</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Talented Student through ETEA</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 380,000</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>ETEA test</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0069</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Youth Scholarship</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>HE Government Colleges in Khyber Pakhtunkhwa</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>possessing good academic merit</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/youth_scholarship</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0063</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Foundation Excellence</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 350,000</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>ETEA test</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0018</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Merit Scholarship</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>University of Agriculture, Dera Ismail Khan</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>-333</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 40,000</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>University of Agriculture, Dera Ismail Khan</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Merit determined from the previous results of two semesters</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R17"/>
+  <autoFilter ref="A1:R32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2080,7 +3444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2198,7 +3562,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0002</t>
+          <t>SCH-202610-0071</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -2288,7 +3652,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0001</t>
+          <t>SCH-202610-0070</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -2378,22 +3742,22 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0022</t>
+          <t>SCH-202610-0065</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>University of Peshawar Need-Based &amp; Fee Waiver Aid 2026-27</t>
+          <t>MORA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>University of Peshawar Students Financial Aid Office</t>
+          <t>Ministry of Religious Affairs &amp; Interfaith Harmony</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>federal govt</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2403,15 +3767,15 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>75</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2421,37 +3785,37 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>50% to 100% tuition fee waiver</t>
+          <t>Rs. 60,000</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>University of Peshawar (UoP)</t>
+          <t>government educational institutions in Pakistan</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate (BS 4-Year), Master's, MPhil, PhD</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Satisfactory academic performance and attendance</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>PKR 50,000 per month</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>https://www.uop.edu.pk/sfao/apply</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2461,29 +3825,29 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>https://www.uop.edu.pk/sfao/</t>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0023</t>
+          <t>SCH-202610-0009</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>UET Peshawar Directorate of Financial Aid Need-cum-Merit Scholarship</t>
+          <t>Rehmatul Lil Alameen Scholarship for Dini Madaris 2026 (رحمت اللعالمین ﷺ اسکالرشپ برائے دینی مدارس)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>University of Engineering and Technology Peshawar</t>
+          <t>Auqaf, Hajj, Religious &amp; Minority Affairs Department</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>university</t>
+          <t>provincial govt</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -2493,15 +3857,15 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2027-03-25</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>159</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2511,37 +3875,37 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Full tuition fee reimbursement plus semester book allowance</t>
+          <t>Rs. 100,000</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>UET Peshawar (Main &amp; satellite campuses)</t>
+          <t>Registered Dini Madaris of Khyber Pakhtunkhwa</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>BSc Engineering, Computer Science, Architecture</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Minimum 2.50 CGPA in previous semester</t>
+          <t>Merit-based</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>PKR 55,000 per month</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>https://uetpeshawar.edu.pk/financial-aid/</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2551,45 +3915,43 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>https://uetpeshawar.edu.pk/financial-aid/</t>
+          <t>https://scholarships.kpitb.online/#laptopScheme</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0004</t>
+          <t>SCH-202610-0054</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ihsan Trust Qarz-e-Hasna Facility for Higher Education</t>
+          <t>KPEF</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Ihsan Trust</t>
+          <t>KP Government / KP Education Foundation</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>NGO-foundation</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Rolling / ongoing</t>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Rolling / ongoing</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
+          <t>2028-12-01</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>776</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -2608,22 +3970,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100% tuition fee loan paid directly to the university</t>
+          <t>Rs. 70</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Over 150 partner universities including public and private universities in KP</t>
+          <t>Agriculture University Swat</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate, Postgraduate</t>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Good academic performance with minimum 2.50 CGPA</t>
+          <t>minimum of 3 GPA</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -2633,7 +3995,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>https://www.ihsantrust.org/apply-now/</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2643,49 +4005,47 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>https://www.ihsantrust.org/education-loan/</t>
+          <t>https://scholarships.kpitb.online/scholarships</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0018</t>
+          <t>SCH-202610-0082</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>75th Celebration of Independence Day of Pakistan Scholarship Program</t>
+          <t>University of Peshawar Need-Based &amp; Fee Waiver Aid 2026-27</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Government of Pakistan</t>
+          <t>University of Peshawar Students Financial Aid Office</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>federal govt</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2695,37 +4055,37 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>50% to 100% tuition fee waiver</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>world's top 25 ranked universities</t>
+          <t>University of Peshawar (UoP)</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>MS and PhD</t>
+          <t>Undergraduate (BS 4-Year), Master's, MPhil, PhD</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>world's top 25 ranked universities</t>
+          <t>Satisfactory academic performance and attendance</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>PKR 50,000 per month</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>https://eportal.hec.gov.pk/idps75</t>
+          <t>https://www.uop.edu.pk/sfao/apply</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2735,49 +4095,47 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>https://www.hec.gov.pk/english/scholarshipsgrants/IDPS/Pages/default.aspx</t>
+          <t>https://www.uop.edu.pk/sfao/</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0008</t>
+          <t>SCH-202610-0083</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CM Foreign Scholarship</t>
+          <t>UET Peshawar Directorate of Financial Aid Need-cum-Merit Scholarship</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+          <t>University of Engineering and Technology Peshawar</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>provincial govt</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
+          <t>2026-11-20</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2787,37 +4145,37 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Full tuition fee reimbursement plus semester book allowance</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>UET Peshawar (Main &amp; satellite campuses)</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>BSc Engineering, Computer Science, Architecture</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Minimum 2.50 CGPA in previous semester</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>PKR 55,000 per month</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+          <t>https://uetpeshawar.edu.pk/financial-aid/</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2827,39 +4185,39 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/</t>
+          <t>https://uetpeshawar.edu.pk/financial-aid/</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0017</t>
+          <t>SCH-202610-0073</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Chief Minister Foreign Scholarship Program</t>
+          <t>Ihsan Trust Qarz-e-Hasna Facility for Higher Education</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Chief Minister of Khyber Pakhtunkhwa through Khyber Pakhtunkhwa Education Foundation</t>
+          <t>Ihsan Trust</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>provincial govt</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Deadline not stated</t>
+          <t>NGO-foundation</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Rolling / ongoing</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Rolling / ongoing</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2884,22 +4242,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>100% tuition fee loan paid directly to the university</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>selected universities in the People's Republic of China</t>
+          <t>Over 150 partner universities including public and private universities in KP</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Language &amp; Culture, BS, MS, and PhD Programs</t>
+          <t>Undergraduate, Postgraduate</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>merit cum in-affordability basis</t>
+          <t>Good academic performance with minimum 2.50 CGPA</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -2909,7 +4267,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>https://www.ihsantrust.org/apply-now/</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2919,29 +4277,29 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
+          <t>https://www.ihsantrust.org/education-loan/</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0012</t>
+          <t>SCH-202610-0079</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Chief Minister's Free Laptop Distribution Scheme</t>
+          <t>75th Celebration of Independence Day of Pakistan Scholarship Program</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Higher Education, Archives and Libraries Department</t>
+          <t>Government of Pakistan</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>provincial govt</t>
+          <t>federal govt</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2981,17 +4339,17 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>approved universities/colleges</t>
+          <t>world's top 25 ranked universities</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>MS and PhD</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>100% merit-based distribution, high-achieving and deserving enrolled students</t>
+          <t>world's top 25 ranked universities</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -3001,7 +4359,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>https://scholarships.kpitb.online/student/laptop</t>
+          <t>https://eportal.hec.gov.pk/idps75</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3011,29 +4369,29 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>https://scholarships.kpitb.online/</t>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/IDPS/Pages/default.aspx</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0019</t>
+          <t>SCH-202610-0075</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Faculty Development Programme for Pakistani Universities</t>
+          <t>CM Foreign Scholarship</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Higher Education Commission, Pakistan</t>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>federal govt</t>
+          <t>provincial govt</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3073,12 +4431,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>HEC recognized universities/DAIs</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3093,7 +4451,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/FDP.aspx</t>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3103,24 +4461,24 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/default.aspx</t>
+          <t>https://ef.kp.gov.pk/</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0009</t>
+          <t>SCH-202610-0006</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>KP Youth Scholarship</t>
+          <t>Chief Minister Foreign Scholarship Program</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+          <t>Government of Khyber Pakhtunkhwa / Khyber Pakhtunkhwa Education Foundation</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3165,17 +4523,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>HE Government Colleges in Khyber Pakhtunkhwa</t>
+          <t>selected universities in the People's Republic of China</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>not stated</t>
+          <t>Language &amp; Culture, BS, MS, and PhD Programs</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>good academic merit</t>
+          <t>merit cum in-affordability basis</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -3185,7 +4543,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/youth_scholarship</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3195,24 +4553,24 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/</t>
+          <t>https://ef.kp.gov.pk/scholarship/cm_foreign_scholarship</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0007</t>
+          <t>SCH-202610-0003</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Merit Cum Inaffordability Scholarship</t>
+          <t>Chief Minister's Free Laptop Distribution Scheme</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+          <t>Higher Education, Archives and Libraries Department</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3227,11 +4585,13 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>-305</v>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -3255,27 +4615,27 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>approved list of Educational Institutions (Available on official website) within Pakistan</t>
+          <t>approved universities/colleges</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>BS &amp; MS</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Student must have scored at least 70% marks in the last attended examination or 3.00 CGPA in each semester, in case of arts specialized university selection will be on the basis of merit aptitude test where selection is on the basis of skills.</t>
+          <t>100% merit-based distribution across all 35 KP districts and approved universities/colleges</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Rs: 160,000/- per month</t>
+          <t>not stated</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/scholarship/merit_cum_inaffordability</t>
+          <t>https://scholarships.kpitb.online/student/laptop</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3285,104 +4645,840 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>https://ef.kp.gov.pk/</t>
+          <t>https://scholarships.kpitb.online/</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0014</t>
+          <t>SCH-202610-0022</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Türkiye Scholarships</t>
+          <t>Chief Minister's Honhaar Scholarship Program</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Türkiye Scholarships (YTB)</t>
+          <t>Bacha Khan University</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>university</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 91,550</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Bacha Khan University</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0080</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Faculty Development Programme for Pakistani Universities</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission, Pakistan</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>federal govt</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Deadline not stated</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6.500 TL at Associate's and Bachelor's levels, 9.500 TL at Master's level and 13.000 TL at PhD level per month.</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>prestigious universities in Türkiye</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>associate, bachelor's, master’s, PhD and research degrees</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>The scholarship program is competitive and merit-based, with a strong emphasis on candidates’ academic excellence</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>https://tbbs.turkiyeburslari.gov.tr</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>HEC recognized universities/DAIs</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/FDP.aspx</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>https://turkiyeburslari.gov.tr/</t>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/default.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0060</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Girls Stipend Programme</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 4,500</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>80% attendance</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0067</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>HEC Internation National Scholarships</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/InternationalScholarships.aspx</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0066</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>HEC National Scholarships</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Higher Education Commission</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>federal govt</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hec.gov.pk/english/scholarshipsgrants/Pages/NationalScholarships.aspx</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0059</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Rehmat Ul Lil Alamin</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 50,000</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0058</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Stoori Da Pakhtunkhwa Program</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 15,000</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Top twenty position holders of Government Schools in SSC and HSSC exams</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0057</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Talented Student through ETEA</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Elementary &amp; Secondary Education</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>August 16, 1947</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 380,000</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>ETEA test</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0069</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Youth Scholarship</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Khyber Pakhtunkhwa Education Foundation (KPEF)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>HE Government Colleges in Khyber Pakhtunkhwa</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>possessing good academic merit</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>https://ef.kp.gov.pk/scholarship/youth_scholarship</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R14"/>
+  <autoFilter ref="A1:R22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3393,7 +5489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3516,12 +5612,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Chevening Pakistan Scholarships 2026-27</t>
+          <t>Türkiye Scholarships</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UK Foreign, Commonwealth and Development Office (FCDO)</t>
+          <t>Türkiye Scholarships / YTB</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -3529,18 +5625,20 @@
           <t>international</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Deadline not stated</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>19</v>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -3559,22 +5657,22 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Fully funded: University tuition fees, monthly living stipend, return economy flights, arrival allowance</t>
+          <t>6.500 TL at Associate's and Bachelor's levels, 9.500 TL at Master's level and 13.000 TL at PhD level per month.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>All accredited UK Universities</t>
+          <t>Turkish universities</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>One-year taught Master's degree</t>
+          <t>associate, bachelor's, master’s, PhD and research degrees</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Undergraduate degree equivalent to UK upper second-class 2:1 honours</t>
+          <t>competitive and merit-based, with a strong emphasis on candidates’ academic excellence</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -3584,7 +5682,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>https://www.chevening.org/scholarship/pakistan/</t>
+          <t>https://tbbs.turkiyeburslari.gov.tr</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -3594,104 +5692,194 @@
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>https://www.chevening.org/scholarship/pakistan/</t>
+          <t>https://turkiyeburslari.gov.tr/</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0016</t>
+          <t>SCH-202610-0074</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>Chevening Pakistan Scholarships 2026-27</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>UK Foreign, Commonwealth and Development Office (FCDO)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Fully funded: University tuition fees, monthly living stipend, return economy flights, arrival allowance</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>All accredited UK Universities</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>One-year taught Master's degree</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Undergraduate degree equivalent to UK upper second-class 2:1 honours</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chevening.org/scholarship/pakistan/</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.chevening.org/scholarship/pakistan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0078</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>Commonwealth Scholarship Programme (Master’s &amp; PhD)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Commonwealth / Higher Education Commission Pakistan</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>international</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Deadline not stated</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Master’s &amp; PhD</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>HEC accepts valid test score of HAT</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>not stated</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>https://www.hec.gov.pk/english/HECAnnouncements/Pages/CW-Scholarship.aspx</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Confirmed</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>https://www.hec.gov.pk/english/scholarshipsgrants/lao/Pages/default.aspx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R3"/>
+  <autoFilter ref="A1:R4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3702,7 +5890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3820,7 +6008,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SCH-202610-0021</t>
+          <t>SCH-202610-0012</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -3849,7 +6037,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-751</v>
+        <v>-752</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -3873,7 +6061,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>colleges or universities in Pakistan and universities across the United States</t>
+          <t>colleges or universities in Pakistan</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -3907,8 +6095,280 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0013</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>U.S. - Pakistan Professional Partnership Program for Journalists</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>United States Educational Foundation in Pakistan</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Previous cycle – awaiting new call</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2020-07-20</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>-2280</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Currently working as a journalist with three to ten years of active experience in journalism with any media organization</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>https://usefp.org/scholarships/journalism.cfm</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>https://usefp.org/scholarships/journalism.cfm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0064</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>KPCIP FULLYFUNDED SCHOLARSHIP</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Khyber Pakhtunkhwa Cities Improvement Project (KPCIP), LGE&amp;RDD</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>provincial govt</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Previous cycle – awaiting new call</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>-849</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Rs. 0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Master's</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>dynamic candidates</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>https://scholarships.kpitb.online/scholarships</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SCH-202610-0068</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Community College Initiative Program (CCIP)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>United States Educational Foundation in Pakistan (USEFP)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Previous cycle – awaiting new call</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>November 20, 2019</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>accredited U.S. community colleges</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>non-degree study (vocational certificate)</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>English language proficiency, potential to have a positive impact on Pakistan's future development and demonstrated leadership</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>https://usefp.org/scholarships/ccip.cfm</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>https://usefp.org/scholarships/ccip.cfm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R2"/>
+  <autoFilter ref="A1:R5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3958,7 +6418,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-17 07:59 PKT</t>
+          <t>2026-10-17 08:21 PKT</t>
         </is>
       </c>
     </row>
@@ -3970,7 +6430,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RUN-20261017-075906</t>
+          <t>RUN-20261017-082108</t>
         </is>
       </c>
     </row>
@@ -3981,7 +6441,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -3991,7 +6451,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -4001,7 +6461,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -4021,7 +6481,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -4031,7 +6491,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -4052,7 +6512,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
